--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-21T06:07:01+00:00</t>
+    <t>2024-10-25T08:29:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2601" uniqueCount="487">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-25T08:29:24+00:00</t>
+    <t>2024-10-29T09:40:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,27 +455,33 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Encounter.extension:Altersgruppe</t>
+    <t>Encounter.extension:altersgruppe</t>
+  </si>
+  <si>
+    <t>altersgruppe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-altersgruppe}
+</t>
   </si>
   <si>
     <t>Altersgruppe</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Altersgruppe}
+    <t>Nach dem Alter in Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
+  </si>
+  <si>
+    <t>Encounter.extension:neugeborenes</t>
+  </si>
+  <si>
+    <t>neugeborenes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-neugeborenes}
 </t>
   </si>
   <si>
-    <t>Nach dem Alter in Gruppen eingeteilt, wobei vollendete Lebensjahre ausschlaggebend sind.</t>
-  </si>
-  <si>
-    <t>Encounter.extension:Neugeborenes</t>
-  </si>
-  <si>
     <t>Neugeborenes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-Neugeborenes}
-</t>
   </si>
   <si>
     <t>Ein Patient wird als Neugeborenes bezeichnet, wenn das Alter zum Zugangszeitpunkt auf die Abteilung &lt;28 Tage ist.</t>
@@ -1856,7 +1862,7 @@
   <cols>
     <col min="1" max="1" width="41.58984375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="41.58984375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.41015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="14.19921875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2954,10 +2960,10 @@
         <v>143</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3037,13 +3043,13 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>19</v>
@@ -3065,13 +3071,13 @@
         <v>19</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -3151,14 +3157,14 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
@@ -3180,16 +3186,16 @@
         <v>134</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>19</v>
@@ -3238,7 +3244,7 @@
         <v>19</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3267,10 +3273,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3293,13 +3299,13 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3350,7 +3356,7 @@
         <v>19</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3365,24 +3371,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3408,13 +3414,13 @@
         <v>107</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3443,10 +3449,10 @@
         <v>111</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>19</v>
@@ -3464,7 +3470,7 @@
         <v>19</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>87</v>
@@ -3479,24 +3485,24 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3519,13 +3525,13 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3552,13 +3558,13 @@
         <v>19</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>19</v>
@@ -3576,7 +3582,7 @@
         <v>19</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3594,21 +3600,21 @@
         <v>19</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3631,13 +3637,13 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3664,31 +3670,31 @@
         <v>19</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="Z16" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>184</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3706,21 +3712,21 @@
         <v>19</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3743,16 +3749,16 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3778,13 +3784,13 @@
         <v>19</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>19</v>
@@ -3802,7 +3808,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3817,24 +3823,24 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3857,13 +3863,13 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3890,13 +3896,13 @@
         <v>19</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>19</v>
@@ -3914,7 +3920,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3929,28 +3935,28 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3969,16 +3975,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4028,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -4043,24 +4049,24 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4083,16 +4089,16 @@
         <v>19</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4122,7 +4128,7 @@
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -4140,7 +4146,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4169,10 +4175,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4195,13 +4201,13 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4252,7 +4258,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4270,25 +4276,25 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4307,13 +4313,13 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4364,7 +4370,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4379,13 +4385,13 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>19</v>
@@ -4393,10 +4399,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4419,13 +4425,13 @@
         <v>19</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4476,7 +4482,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4497,7 +4503,7 @@
         <v>19</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>19</v>
@@ -4505,10 +4511,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4531,16 +4537,16 @@
         <v>19</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4590,7 +4596,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4605,13 +4611,13 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>19</v>
@@ -4619,10 +4625,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4645,13 +4651,13 @@
         <v>19</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4702,7 +4708,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4717,24 +4723,24 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4757,16 +4763,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4816,7 +4822,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4828,27 +4834,27 @@
         <v>19</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4871,13 +4877,13 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4928,7 +4934,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4937,7 +4943,7 @@
         <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AJ27" t="s" s="2">
         <v>19</v>
@@ -4949,7 +4955,7 @@
         <v>19</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>19</v>
@@ -4957,14 +4963,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4986,13 +4992,13 @@
         <v>134</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5042,7 +5048,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -5063,7 +5069,7 @@
         <v>19</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>19</v>
@@ -5071,14 +5077,14 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5100,16 +5106,16 @@
         <v>134</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5158,7 +5164,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5187,10 +5193,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5213,16 +5219,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5248,31 +5254,31 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
+        <v>286</v>
+      </c>
+      <c r="Y30" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="Y30" t="s" s="2">
+      <c r="Z30" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="AF30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="Z30" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="AA30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AB30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AC30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AD30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AE30" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="AF30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5281,30 +5287,30 @@
         <v>78</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5327,13 +5333,13 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -5384,7 +5390,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5405,18 +5411,18 @@
         <v>19</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5439,16 +5445,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5498,7 +5504,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5507,30 +5513,30 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5553,13 +5559,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5610,7 +5616,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5625,24 +5631,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5665,16 +5671,16 @@
         <v>19</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5724,7 +5730,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5753,10 +5759,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5779,16 +5785,16 @@
         <v>19</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5838,7 +5844,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5853,24 +5859,24 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5893,13 +5899,13 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5950,7 +5956,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5974,15 +5980,15 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6005,13 +6011,13 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6062,7 +6068,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -6086,15 +6092,15 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6117,16 +6123,16 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6176,7 +6182,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6191,24 +6197,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6231,16 +6237,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6290,7 +6296,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6319,10 +6325,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6345,13 +6351,13 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6402,7 +6408,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>77</v>
@@ -6411,7 +6417,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>19</v>
@@ -6423,7 +6429,7 @@
         <v>19</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>19</v>
@@ -6431,14 +6437,14 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6460,13 +6466,13 @@
         <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6516,7 +6522,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6537,7 +6543,7 @@
         <v>19</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>19</v>
@@ -6545,14 +6551,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6574,16 +6580,16 @@
         <v>134</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6632,7 +6638,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6661,10 +6667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6687,13 +6693,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6720,11 +6726,11 @@
         <v>19</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>19</v>
@@ -6742,7 +6748,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -6771,14 +6777,14 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6797,13 +6803,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6830,13 +6836,13 @@
         <v>19</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>19</v>
@@ -6854,7 +6860,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -6869,24 +6875,24 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6909,16 +6915,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6968,7 +6974,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6989,7 +6995,7 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>19</v>
@@ -6997,10 +7003,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7023,13 +7029,13 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7080,7 +7086,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7089,7 +7095,7 @@
         <v>87</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>19</v>
@@ -7101,7 +7107,7 @@
         <v>19</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>19</v>
@@ -7109,14 +7115,14 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7138,13 +7144,13 @@
         <v>134</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7194,7 +7200,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -7215,7 +7221,7 @@
         <v>19</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>19</v>
@@ -7223,14 +7229,14 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -7252,16 +7258,16 @@
         <v>134</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7310,7 +7316,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7339,14 +7345,14 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7365,13 +7371,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7398,11 +7404,11 @@
         <v>19</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>19</v>
@@ -7420,7 +7426,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7435,24 +7441,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7475,13 +7481,13 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7508,13 +7514,13 @@
         <v>19</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>19</v>
@@ -7532,7 +7538,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7553,18 +7559,18 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7587,16 +7593,16 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7646,7 +7652,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7667,7 +7673,7 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>19</v>
@@ -7675,10 +7681,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7701,19 +7707,19 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -7738,13 +7744,13 @@
         <v>19</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -7762,7 +7768,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -7783,18 +7789,18 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7817,13 +7823,13 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7850,13 +7856,13 @@
         <v>19</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>19</v>
@@ -7874,7 +7880,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7895,18 +7901,18 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7929,16 +7935,16 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7964,13 +7970,13 @@
         <v>19</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>19</v>
@@ -7988,7 +7994,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8009,18 +8015,18 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8043,16 +8049,16 @@
         <v>19</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8102,7 +8108,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8123,7 +8129,7 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>19</v>
@@ -8131,10 +8137,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8157,13 +8163,13 @@
         <v>19</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8214,7 +8220,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8223,7 +8229,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>19</v>
@@ -8235,7 +8241,7 @@
         <v>19</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>19</v>
@@ -8243,14 +8249,14 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8272,13 +8278,13 @@
         <v>134</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8328,7 +8334,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8349,7 +8355,7 @@
         <v>19</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>19</v>
@@ -8357,14 +8363,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8386,16 +8392,16 @@
         <v>134</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>19</v>
@@ -8444,7 +8450,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8473,10 +8479,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8499,13 +8505,13 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8556,7 +8562,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8577,18 +8583,18 @@
         <v>19</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8611,13 +8617,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8668,7 +8674,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8689,7 +8695,7 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>19</v>
@@ -8697,10 +8703,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8723,13 +8729,13 @@
         <v>19</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8756,13 +8762,13 @@
         <v>19</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>19</v>
@@ -8780,7 +8786,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8801,18 +8807,18 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8835,13 +8841,13 @@
         <v>19</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8868,13 +8874,13 @@
         <v>19</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>19</v>
@@ -8892,7 +8898,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -8913,18 +8919,18 @@
         <v>19</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8947,13 +8953,13 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -9004,7 +9010,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9025,18 +9031,18 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9059,13 +9065,13 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9096,7 +9102,7 @@
       </c>
       <c r="Y64" s="2"/>
       <c r="Z64" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>19</v>
@@ -9114,7 +9120,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9135,18 +9141,18 @@
         <v>19</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9169,16 +9175,16 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9228,7 +9234,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9249,7 +9255,7 @@
         <v>19</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>19</v>
@@ -9257,10 +9263,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9283,13 +9289,13 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9340,7 +9346,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9349,7 +9355,7 @@
         <v>87</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>19</v>
@@ -9361,7 +9367,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9369,14 +9375,14 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9398,13 +9404,13 @@
         <v>134</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9454,7 +9460,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9475,7 +9481,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9483,14 +9489,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -9512,16 +9518,16 @@
         <v>134</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -9570,7 +9576,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9599,10 +9605,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9625,13 +9631,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9682,7 +9688,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>87</v>
@@ -9697,24 +9703,24 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9740,13 +9746,13 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9775,10 +9781,10 @@
         <v>111</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>19</v>
@@ -9796,7 +9802,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9817,7 +9823,7 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>19</v>
@@ -9825,10 +9831,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9851,16 +9857,16 @@
         <v>19</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9886,13 +9892,13 @@
         <v>19</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>19</v>
@@ -9910,7 +9916,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9939,10 +9945,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9965,13 +9971,13 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10022,7 +10028,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -10043,7 +10049,7 @@
         <v>19</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>19</v>

--- a/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
+++ b/r5-ELGA-MOPED-126-changes-for-pysische-anwesenheit/StructureDefinition-MOPEDTransferEncounter.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:40:57+00:00</t>
+    <t>2024-10-29T10:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
